--- a/RO.xlsx
+++ b/RO.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/esp1/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3286FB3F-ED5C-D540-957A-3309DFAE904F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66805003-CB69-FA4A-B4C1-C533D6E02216}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10460" yWindow="900" windowWidth="33600" windowHeight="19020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="33600" windowHeight="19020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RO Liste" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1412" uniqueCount="688">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1416" uniqueCount="691">
   <si>
     <t>Fornavn</t>
   </si>
@@ -2077,13 +2077,22 @@
     <t>einar@dssn.no</t>
   </si>
   <si>
-    <t>esp1@dssn.no</t>
-  </si>
-  <si>
     <t>Klubb</t>
   </si>
   <si>
     <t>Region</t>
+  </si>
+  <si>
+    <t>esp1+ro@dssn.no</t>
+  </si>
+  <si>
+    <t>Ola (test)</t>
+  </si>
+  <si>
+    <t>Nordmann (test)</t>
+  </si>
+  <si>
+    <t>espen.fiskebeck@gmail.com</t>
   </si>
 </sst>
 </file>
@@ -2471,13 +2480,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F469"/>
+  <dimension ref="A1:F470"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
     <col min="2" max="2" width="25" customWidth="1"/>
     <col min="3" max="3" width="30" customWidth="1"/>
-    <col min="4" max="4" width="12.5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="22.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.2">
@@ -2494,10 +2503,10 @@
         <v>683</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>685</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>686</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>687</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
@@ -6606,7 +6615,7 @@
         <v>5</v>
       </c>
       <c r="D374" s="6" t="s">
-        <v>685</v>
+        <v>687</v>
       </c>
     </row>
     <row r="375" spans="1:4" x14ac:dyDescent="0.2">
@@ -7599,7 +7608,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="465" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="465" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A465" s="4" t="s">
         <v>262</v>
       </c>
@@ -7610,7 +7619,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="466" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="466" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A466" s="2" t="s">
         <v>547</v>
       </c>
@@ -7621,7 +7630,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="467" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="467" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A467" s="2" t="s">
         <v>68</v>
       </c>
@@ -7632,7 +7641,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="468" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="468" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A468" s="4" t="s">
         <v>680</v>
       </c>
@@ -7643,7 +7652,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="469" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="469" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A469" s="2" t="s">
         <v>41</v>
       </c>
@@ -7652,12 +7661,27 @@
       </c>
       <c r="C469" s="2" t="s">
         <v>5</v>
+      </c>
+    </row>
+    <row r="470" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A470" s="2" t="s">
+        <v>688</v>
+      </c>
+      <c r="B470" s="2" t="s">
+        <v>689</v>
+      </c>
+      <c r="C470" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D470" s="6" t="s">
+        <v>690</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="D35" r:id="rId1" xr:uid="{FC312CC9-6D63-FF4E-B154-B3E2290D6DB0}"/>
-    <hyperlink ref="D374" r:id="rId2" xr:uid="{FB3298C0-BA2E-0446-9FC4-4B3088CAF3A0}"/>
+    <hyperlink ref="D374" r:id="rId2" xr:uid="{7DCA5473-B1BA-4345-9F92-895ED1E35BEF}"/>
+    <hyperlink ref="D470" r:id="rId3" xr:uid="{12A016F2-C045-9342-B298-020DDE9D62D2}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
